--- a/interfaz/backend/static/plantilla_pedidos_historicos.xlsx
+++ b/interfaz/backend/static/plantilla_pedidos_historicos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe54d4b8f6e414bb/Escritorio/MARTA/UPV/EMPLEA/Reto-EMPLEA-El-Corte-Ingles/interfaz/backend/static/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe54d4b8f6e414bb/Escritorio/MARTA/UPV/EMPLEA/DEFINITIVO 20-08-2026/Reto-EMPLEA-El-Corte-Ingles/interfaz/backend/static/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D011E395-EE23-48C3-AF63-A783C41D4DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{D011E395-EE23-48C3-AF63-A783C41D4DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0018E1B1-0233-4717-A05E-D0413C9555C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C0BB50A6-DB9C-43AE-8DCC-A2140289EBAB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Fecha de venta</t>
   </si>
@@ -211,6 +211,9 @@
       </rPr>
       <t>LÍNEAS</t>
     </r>
+  </si>
+  <si>
+    <t>Devoluciones</t>
   </si>
 </sst>
 </file>
@@ -290,12 +293,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -325,9 +329,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B9C6E65B-A28D-4AD8-8C48-E819713E704E}" name="Tabla1" displayName="Tabla1" ref="A1:K19" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:K19" xr:uid="{B9C6E65B-A28D-4AD8-8C48-E819713E704E}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B9C6E65B-A28D-4AD8-8C48-E819713E704E}" name="Tabla1" displayName="Tabla1" ref="A1:L19" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:L19" xr:uid="{B9C6E65B-A28D-4AD8-8C48-E819713E704E}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{B7B54DDA-E21C-4E64-86BB-0CED12D434B4}" name="Fecha de venta"/>
     <tableColumn id="2" xr3:uid="{CE85D443-089F-4800-8009-4D23D329EBC7}" name="Núm. pedidos 2h MCIA GENERAL"/>
     <tableColumn id="3" xr3:uid="{1699F9FB-BDF8-4B34-B035-F2686062F34A}" name="Núm. Líneas 2h MCIA GENERAL"/>
@@ -339,6 +343,7 @@
     <tableColumn id="9" xr3:uid="{BC80646B-7D4E-4635-9457-8F4D491EE6B4}" name="Núm. líneas HOME DELIVERY"/>
     <tableColumn id="10" xr3:uid="{F403A357-A4A2-47B1-B527-D9A68BA483E9}" name="Total PEDIDOS"/>
     <tableColumn id="11" xr3:uid="{F686688A-CF98-4376-8991-4EA970C3FA45}" name="Total LÍNEAS"/>
+    <tableColumn id="13" xr3:uid="{C6ABA44F-46FF-4783-A88E-8F8474B79136}" name="Devoluciones"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -661,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5D4C65-5968-4D4B-93CE-91D56C081376}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -675,9 +680,10 @@
     <col min="9" max="9" width="36.88671875" customWidth="1"/>
     <col min="10" max="10" width="19.77734375" customWidth="1"/>
     <col min="11" max="11" width="17.77734375" customWidth="1"/>
+    <col min="12" max="12" width="24.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" ht="18">
+    <row r="1" spans="1:12" s="4" customFormat="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -710,6 +716,9 @@
       </c>
       <c r="K1" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
